--- a/tracking_forms/037_food_calorie_tracking_log--tracking_forms.xlsx
+++ b/tracking_forms/037_food_calorie_tracking_log--tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -753,7 +753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>coaching</t>
+          <t>cooking</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Coaching</t>
+          <t>Cooking</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>coaching</t>
+          <t>foodie</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Coaching</t>
+          <t>Foodie</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>cooking</t>
+          <t>health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cooking</t>
+          <t>Health</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>foodie</t>
+          <t>nutrition</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Foodie</t>
+          <t>Nutrition</t>
         </is>
       </c>
     </row>
@@ -1228,267 +1228,63 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>health</t>
+          <t>wellness</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Wellness</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>user_category_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nutrition</t>
+          <t>client</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nutrition</t>
+          <t>Client</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>user_category_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>wellness</t>
+          <t>coach</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wellness</t>
+          <t>Coach</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>user_category_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>wellness</t>
+          <t>user</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wellness</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>wellness</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Wellness</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>wellness</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Wellness</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>wellness</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Wellness</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>user_category_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>client</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Client</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>user_category_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>coach</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Coach</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>user_category_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>client</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Client</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>user_category_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>coach</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Coach</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>user_category_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>client</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Client</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>user_category_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>coach</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Coach</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>user_category_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>coach</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Coach</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>user_category_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>user</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
           <t>User</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>user_category_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>client</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Client</t>
         </is>
       </c>
     </row>
